--- a/03_Screening/Screening_Audit_Summary_2026-09-15.xlsx
+++ b/03_Screening/Screening_Audit_Summary_2026-09-15.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,6 +26,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
     </font>
   </fonts>
@@ -55,11 +61,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,79 +433,471 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>PRISMA 2020 Flow Stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Percentage / Sub-breakdown</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Notes / Methodological Rules</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total Unique Records Screened (PRISMA Box 3)</t>
+          <t>Total Records Identified across Databases (PRISMA Box 1)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7283</v>
+        <v>9112</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Google Scholar: 5,747; OpenAlex: 2,802; DOAJ: 419; AJOL: 144</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Records Excluded at Title/Abstract Phase (PRISMA Box 4)</t>
+          <t>Duplicate Records Removed (PRISMA Box 2)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4461</v>
+        <v>1829</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Exact DOI matching: 514; Fuzzy Title/Author matching (Levenshtein &gt;= 0.90): 1,315</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Excluded: Non-material or non-construction focus (EX-MAT)</t>
+          <t>Total Unique Records Screened at Title/Abstract (PRISMA Box 3)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4311</v>
+        <v>7283</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>79.9%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Net unique records evaluated against title/abstract PICO criteria</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Excluded: Non-African geographic setting (EX-GEO)</t>
+          <t>Records Excluded at Title/Abstract Phase (PRISMA Box 4)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>148</v>
+        <v>4461</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>61.3%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Excluded by predefined inclusion/exclusion criteria:</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Excluded: Non-empirical document type (EX-TYPE)</t>
+          <t xml:space="preserve">  - Excluded: Non-material or non-construction focus (EX-MAT)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4311</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>59.2%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Agricultural fertilizers, water filtration, medical biomaterials, pure chemistry</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Studies Sought for Full-Text Retrieval (PRISMA Box 5 Candidate)</t>
+          <t xml:space="preserve">  - Excluded: Non-African geographic setting (EX-GEO)</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>148</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Explicit non-African settings identifiable at title/abstract phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Excluded: Non-empirical document type (EX-TYPE)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>&lt;0.1%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>News bulletins, conference announcements, or editorial notices</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Full-Text Records Sought for Retrieval &amp; Assessed (PRISMA Box 5)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>2822</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>38.7%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Candidate records advancing to full-text retrieval and eligibility assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Full-Text Records Excluded with Reasons (PRISMA Box 6)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>330</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11.7%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Screened against full-text eligibility criteria:</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Excluded: Secondary reviews / bibliometrics / books (EX-DOCTYPE)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>231</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8.2%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Reviews, scoping overviews, meta-analyses, bibliometrics, and book chapters</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Excluded: Non-African geographic setting &amp; feedstocks (EX-GEO)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>84</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Studies from South America, Asia, Europe without African feedstocks/context</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Excluded: Non-building / out-of-scope applications (EX-MAT)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Asphalt wearing courses, pavement binders, wastewater adsorption</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Excluded: Non-English publication without translation (EX-LANG)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>&lt;0.1%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Foreign language records lacking English text</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Final Verified Primary Studies Included in Review (PRISMA Box 7)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2492</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>88.3%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Empirical laboratory trials, field prototypes, and quantitative LCAs included in extraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>DETAILED COMPOSITION OF EX-MAT EXCLUSIONS (n = 4,311)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Agricultural soil science &amp; fertilizer studies</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Soil fertility, crop yields, amendments not involving construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Water treatment &amp; environmental remediation</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Biochar adsorption, wastewater filtration, heavy metal remediation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Pure chemistry &amp; materials science (non-construction)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>620</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>14.4%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Polymer synthesis, nanoparticle characterization, catalyst studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Medical/biomedical applications</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>7.9%</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Bioceramics, bone implants, pharmaceutical encapsulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Food science &amp; packaging</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Biodegradable packaging, food preservation using plant fibers</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Pavement &amp; asphalt engineering</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Highway wearing courses, asphalt binders (non-building scope)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Energy &amp; biofuel applications</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Biomass combustion, pyrolysis, charcoal briquettes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL EX-MAT</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4311</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
     </row>
   </sheetData>
